--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_360_R36.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_360_R36.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>9.9435</v>
+        <v>11.1628</v>
       </c>
       <c r="E2" t="n">
-        <v>7.719</v>
+        <v>8.5014</v>
       </c>
       <c r="F2" t="n">
-        <v>2.2245</v>
+        <v>2.6614</v>
       </c>
       <c r="G2" t="n">
         <v>5.268</v>
@@ -610,13 +610,13 @@
         <v>1.8556</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.3967</v>
+        <v>0.8226</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.7978</v>
+        <v>-0.0154</v>
       </c>
       <c r="U2" t="n">
-        <v>0.4011</v>
+        <v>0.838</v>
       </c>
       <c r="V2" t="n">
         <v>3.2166</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.2898</v>
+        <v>3.8953</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.9709</v>
+        <v>-0.4244</v>
       </c>
       <c r="F3" t="n">
-        <v>5.2607</v>
+        <v>4.3197</v>
       </c>
       <c r="G3" t="n">
         <v>5.041</v>
@@ -688,13 +688,13 @@
         <v>1.6237</v>
       </c>
       <c r="S3" t="n">
-        <v>1.3337</v>
+        <v>0.9392</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.7389</v>
+        <v>-0.1924</v>
       </c>
       <c r="U3" t="n">
-        <v>2.0726</v>
+        <v>1.1317</v>
       </c>
       <c r="V3" t="n">
         <v>0.9304</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.1969</v>
+        <v>3.0555</v>
       </c>
       <c r="E4" t="n">
-        <v>1.7614</v>
+        <v>2.3512</v>
       </c>
       <c r="F4" t="n">
-        <v>0.4354</v>
+        <v>0.7043</v>
       </c>
       <c r="G4" t="n">
         <v>1.2036</v>
@@ -766,13 +766,13 @@
         <v>0.6959</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.1511</v>
+        <v>0.7075</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.2003</v>
+        <v>0.3894</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0492</v>
+        <v>0.3181</v>
       </c>
       <c r="V4" t="n">
         <v>1.6083</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.978</v>
+        <v>0.7153</v>
       </c>
       <c r="E5" t="n">
-        <v>0.4477</v>
+        <v>0.0506</v>
       </c>
       <c r="F5" t="n">
-        <v>0.5303</v>
+        <v>0.6647999999999999</v>
       </c>
       <c r="G5" t="n">
         <v>1.7366</v>
@@ -844,13 +844,13 @@
         <v>0.9278</v>
       </c>
       <c r="S5" t="n">
-        <v>0.5456</v>
+        <v>0.2829</v>
       </c>
       <c r="T5" t="n">
-        <v>0.2715</v>
+        <v>-0.1256</v>
       </c>
       <c r="U5" t="n">
-        <v>0.2741</v>
+        <v>0.4086</v>
       </c>
       <c r="V5" t="n">
         <v>-1.0722</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.458</v>
+        <v>-0.7153</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.7148</v>
+        <v>-2.2914</v>
       </c>
       <c r="F6" t="n">
-        <v>1.1728</v>
+        <v>1.5761</v>
       </c>
       <c r="G6" t="n">
         <v>-0.7249</v>
@@ -922,13 +922,13 @@
         <v>2.0876</v>
       </c>
       <c r="S6" t="n">
-        <v>2.2035</v>
+        <v>1.0302</v>
       </c>
       <c r="T6" t="n">
-        <v>2.0331</v>
+        <v>0.4564</v>
       </c>
       <c r="U6" t="n">
-        <v>0.1705</v>
+        <v>0.5737</v>
       </c>
       <c r="V6" t="n">
         <v>-0.7886</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.287</v>
+        <v>-1.0676</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.6003</v>
+        <v>-1.2464</v>
       </c>
       <c r="F7" t="n">
-        <v>0.3133</v>
+        <v>0.1788</v>
       </c>
       <c r="G7" t="n">
         <v>0.7028</v>
@@ -1000,13 +1000,13 @@
         <v>1.3917</v>
       </c>
       <c r="S7" t="n">
-        <v>0.492</v>
+        <v>0.7114</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.731</v>
+        <v>-0.3771</v>
       </c>
       <c r="U7" t="n">
-        <v>1.223</v>
+        <v>1.0886</v>
       </c>
       <c r="V7" t="n">
         <v>-0.3943</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.4795</v>
+        <v>-1.2526</v>
       </c>
       <c r="E8" t="n">
-        <v>-3.7268</v>
+        <v>-3.2982</v>
       </c>
       <c r="F8" t="n">
-        <v>2.2473</v>
+        <v>2.0456</v>
       </c>
       <c r="G8" t="n">
         <v>-2.5735</v>
@@ -1078,13 +1078,13 @@
         <v>1.3917</v>
       </c>
       <c r="S8" t="n">
-        <v>0.2074</v>
+        <v>0.4343</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.963</v>
+        <v>-0.5344</v>
       </c>
       <c r="U8" t="n">
-        <v>1.1703</v>
+        <v>0.9687</v>
       </c>
       <c r="V8" t="n">
         <v>-0.5051</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.8645</v>
+        <v>-2.1848</v>
       </c>
       <c r="E9" t="n">
-        <v>-3.5247</v>
+        <v>-3.8785</v>
       </c>
       <c r="F9" t="n">
-        <v>1.6602</v>
+        <v>1.6938</v>
       </c>
       <c r="G9" t="n">
         <v>-4.8045</v>
@@ -1156,13 +1156,13 @@
         <v>1.6237</v>
       </c>
       <c r="S9" t="n">
-        <v>1.0328</v>
+        <v>0.7125</v>
       </c>
       <c r="T9" t="n">
-        <v>0.7749</v>
+        <v>0.4211</v>
       </c>
       <c r="U9" t="n">
-        <v>0.2579</v>
+        <v>0.2915</v>
       </c>
       <c r="V9" t="n">
         <v>0.2836</v>
@@ -1189,10 +1189,10 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>13.2352</v>
+        <v>13.6086</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.6094000000000008</v>
+        <v>-0.2357000000000014</v>
       </c>
       <c r="F10" t="n">
         <v>13.8445</v>
@@ -1234,13 +1234,13 @@
         <v>11.5977</v>
       </c>
       <c r="S10" t="n">
-        <v>5.2672</v>
+        <v>5.6406</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.3514999999999997</v>
+        <v>0.02200000000000002</v>
       </c>
       <c r="U10" t="n">
-        <v>5.6187</v>
+        <v>5.6189</v>
       </c>
       <c r="V10" t="n">
         <v>3.278700000000001</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>4.8878</v>
+        <v>5.9779</v>
       </c>
       <c r="E11" t="n">
-        <v>5.5574</v>
+        <v>6.501</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.6696</v>
+        <v>-0.5231</v>
       </c>
       <c r="G11" t="n">
         <v>4.5643</v>
@@ -1312,13 +1312,13 @@
         <v>2.0876</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.8183</v>
+        <v>-0.7281</v>
       </c>
       <c r="T11" t="n">
-        <v>-2.0164</v>
+        <v>-1.0728</v>
       </c>
       <c r="U11" t="n">
-        <v>0.1981</v>
+        <v>0.3446</v>
       </c>
       <c r="V11" t="n">
         <v>1.214</v>
@@ -1333,7 +1333,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>P. EBOUA</t>
+          <t>S. HARRISON</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,64 +1345,64 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>1.6141</v>
+        <v>1.4476</v>
       </c>
       <c r="E12" t="n">
-        <v>1.7654</v>
+        <v>1.4342</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.1514</v>
+        <v>0.0134</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.9075</v>
+        <v>3.2538</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.6399</v>
+        <v>-1.9424</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.2677</v>
+        <v>5.1962</v>
       </c>
       <c r="J12" t="n">
-        <v>0.6832</v>
+        <v>4.437</v>
       </c>
       <c r="K12" t="n">
-        <v>0.1078</v>
+        <v>-1.4985</v>
       </c>
       <c r="L12" t="n">
-        <v>0.5754</v>
+        <v>5.9355</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.5908</v>
+        <v>-1.1833</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.7477</v>
+        <v>-0.4439</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.8431</v>
+        <v>-0.7393999999999999</v>
       </c>
       <c r="P12" t="n">
-        <v>1.8556</v>
+        <v>-1.3917</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>-3.4793</v>
       </c>
       <c r="R12" t="n">
-        <v>1.8556</v>
+        <v>2.0876</v>
       </c>
       <c r="S12" t="n">
-        <v>1.5964</v>
+        <v>-0.8088</v>
       </c>
       <c r="T12" t="n">
-        <v>0.7986</v>
+        <v>-1.1319</v>
       </c>
       <c r="U12" t="n">
-        <v>0.7978</v>
+        <v>0.3231</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.9304</v>
+        <v>0.3943</v>
       </c>
       <c r="W12" t="n">
-        <v>0.2836</v>
+        <v>1.6083</v>
       </c>
       <c r="X12" t="n">
         <v>-1.214</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>S. HARRISON</t>
+          <t>P. EBOUA</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,64 +1423,64 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>0.4768</v>
+        <v>0.3737</v>
       </c>
       <c r="E13" t="n">
-        <v>1.0804</v>
+        <v>0.7039</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.6036</v>
+        <v>-0.3302</v>
       </c>
       <c r="G13" t="n">
-        <v>3.2538</v>
+        <v>-0.9075</v>
       </c>
       <c r="H13" t="n">
-        <v>-1.9424</v>
+        <v>-0.6399</v>
       </c>
       <c r="I13" t="n">
-        <v>5.1962</v>
+        <v>-0.2677</v>
       </c>
       <c r="J13" t="n">
-        <v>4.437</v>
+        <v>0.6832</v>
       </c>
       <c r="K13" t="n">
-        <v>-1.4985</v>
+        <v>0.1078</v>
       </c>
       <c r="L13" t="n">
-        <v>5.9355</v>
+        <v>0.5754</v>
       </c>
       <c r="M13" t="n">
-        <v>-1.1833</v>
+        <v>-1.5908</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.4439</v>
+        <v>-0.7477</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.7393999999999999</v>
+        <v>-0.8431</v>
       </c>
       <c r="P13" t="n">
-        <v>-1.3917</v>
+        <v>1.8556</v>
       </c>
       <c r="Q13" t="n">
-        <v>-3.4793</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>2.0876</v>
+        <v>1.8556</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.7796</v>
+        <v>0.356</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.4857</v>
+        <v>-0.2629</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.2939</v>
+        <v>0.619</v>
       </c>
       <c r="V13" t="n">
-        <v>0.3943</v>
+        <v>-0.9304</v>
       </c>
       <c r="W13" t="n">
-        <v>1.6083</v>
+        <v>0.2836</v>
       </c>
       <c r="X13" t="n">
         <v>-1.214</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.9967</v>
+        <v>-0.8623</v>
       </c>
       <c r="E14" t="n">
         <v>-1.8909</v>
       </c>
       <c r="F14" t="n">
-        <v>0.8941</v>
+        <v>1.0286</v>
       </c>
       <c r="G14" t="n">
         <v>-2.156</v>
@@ -1546,13 +1546,13 @@
         <v>0.4639</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.5983000000000001</v>
+        <v>-0.4639</v>
       </c>
       <c r="T14" t="n">
         <v>-0.8215</v>
       </c>
       <c r="U14" t="n">
-        <v>0.2232</v>
+        <v>0.3576</v>
       </c>
       <c r="V14" t="n">
         <v>1.2937</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-2.1099</v>
+        <v>-1.257</v>
       </c>
       <c r="E15" t="n">
-        <v>-2.5389</v>
+        <v>-2.303</v>
       </c>
       <c r="F15" t="n">
-        <v>0.4291</v>
+        <v>1.0461</v>
       </c>
       <c r="G15" t="n">
         <v>-1.0261</v>
@@ -1624,13 +1624,13 @@
         <v>1.1598</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.0838</v>
+        <v>-0.2309</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.6326000000000001</v>
+        <v>-0.3967</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.4512</v>
+        <v>0.1658</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Z. SELJAAS</t>
+          <t>E. JACKSON</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-2.5905</v>
+        <v>-2.2782</v>
       </c>
       <c r="E16" t="n">
-        <v>-3.8789</v>
+        <v>-1.8492</v>
       </c>
       <c r="F16" t="n">
-        <v>1.2884</v>
+        <v>-0.429</v>
       </c>
       <c r="G16" t="n">
-        <v>-2.8881</v>
+        <v>-0.1512</v>
       </c>
       <c r="H16" t="n">
-        <v>-1.8942</v>
+        <v>-1.1082</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.9939</v>
+        <v>0.9569</v>
       </c>
       <c r="J16" t="n">
-        <v>-3.545</v>
+        <v>-0.4186</v>
       </c>
       <c r="K16" t="n">
-        <v>-1.1358</v>
+        <v>-0.1709</v>
       </c>
       <c r="L16" t="n">
-        <v>-2.4093</v>
+        <v>-0.2477</v>
       </c>
       <c r="M16" t="n">
-        <v>0.657</v>
+        <v>0.2674</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.7584</v>
+        <v>-0.9373</v>
       </c>
       <c r="O16" t="n">
-        <v>1.4154</v>
+        <v>1.2046</v>
       </c>
       <c r="P16" t="n">
-        <v>1.6237</v>
+        <v>0.6959</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R16" t="n">
-        <v>1.6237</v>
+        <v>1.8556</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.2539</v>
+        <v>-0.1423</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.3339</v>
+        <v>-0.2708</v>
       </c>
       <c r="U16" t="n">
-        <v>0.08</v>
+        <v>0.1285</v>
       </c>
       <c r="V16" t="n">
-        <v>-1.0722</v>
+        <v>-2.6805</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.0722</v>
+        <v>-2.6805</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A. TRAORE</t>
+          <t>Z. SELJAAS</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-2.7639</v>
+        <v>-2.3267</v>
       </c>
       <c r="E17" t="n">
-        <v>-3.7788</v>
+        <v>-3.9969</v>
       </c>
       <c r="F17" t="n">
-        <v>1.0149</v>
+        <v>1.6701</v>
       </c>
       <c r="G17" t="n">
-        <v>-2.5179</v>
+        <v>-2.8881</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.7683</v>
+        <v>-1.8942</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.7495000000000001</v>
+        <v>-0.9939</v>
       </c>
       <c r="J17" t="n">
-        <v>-2.2851</v>
+        <v>-3.545</v>
       </c>
       <c r="K17" t="n">
-        <v>-1.5356</v>
+        <v>-1.1358</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.7495000000000001</v>
+        <v>-2.4093</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.2327</v>
+        <v>0.657</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.2327</v>
+        <v>-0.7584</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>1.4154</v>
       </c>
       <c r="P17" t="n">
-        <v>-1.8556</v>
+        <v>1.6237</v>
       </c>
       <c r="Q17" t="n">
-        <v>-2.3195</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>0.4639</v>
+        <v>1.6237</v>
       </c>
       <c r="S17" t="n">
-        <v>1.6096</v>
+        <v>0.009900000000000001</v>
       </c>
       <c r="T17" t="n">
-        <v>0.8259</v>
+        <v>-0.4518</v>
       </c>
       <c r="U17" t="n">
-        <v>0.7837</v>
+        <v>0.4617</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>-1.0722</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>E. JACKSON</t>
+          <t>B. MASSA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-3.2047</v>
+        <v>-3.7684</v>
       </c>
       <c r="E18" t="n">
-        <v>-2.2031</v>
+        <v>-3.1828</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.0017</v>
+        <v>-0.5856</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.1512</v>
+        <v>-1.9232</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.1082</v>
+        <v>-2.8835</v>
       </c>
       <c r="I18" t="n">
-        <v>0.9569</v>
+        <v>0.9603</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.4186</v>
+        <v>-1.6261</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.1709</v>
+        <v>-2.3254</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.2477</v>
+        <v>0.6993</v>
       </c>
       <c r="M18" t="n">
-        <v>0.2674</v>
+        <v>-0.297</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.9373</v>
+        <v>-0.5581</v>
       </c>
       <c r="O18" t="n">
-        <v>1.2046</v>
+        <v>0.261</v>
       </c>
       <c r="P18" t="n">
-        <v>0.6959</v>
+        <v>-0.6959</v>
       </c>
       <c r="Q18" t="n">
         <v>-1.1598</v>
       </c>
       <c r="R18" t="n">
-        <v>1.8556</v>
+        <v>0.4639</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.0688</v>
+        <v>-0.8659</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.6247</v>
+        <v>-0.3969</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.4441</v>
+        <v>-0.4689</v>
       </c>
       <c r="V18" t="n">
-        <v>-2.6805</v>
+        <v>-0.2836</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-2.6805</v>
+        <v>-0.2836</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>B. MASSA</t>
+          <t>A. TRAORE</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-4.1673</v>
+        <v>-3.9763</v>
       </c>
       <c r="E19" t="n">
-        <v>-3.3007</v>
+        <v>-4.7224</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.8666</v>
+        <v>0.746</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.9232</v>
+        <v>-2.5179</v>
       </c>
       <c r="H19" t="n">
-        <v>-2.8835</v>
+        <v>-1.7683</v>
       </c>
       <c r="I19" t="n">
-        <v>0.9603</v>
+        <v>-0.7495000000000001</v>
       </c>
       <c r="J19" t="n">
-        <v>-1.6261</v>
+        <v>-2.2851</v>
       </c>
       <c r="K19" t="n">
-        <v>-2.3254</v>
+        <v>-1.5356</v>
       </c>
       <c r="L19" t="n">
-        <v>0.6993</v>
+        <v>-0.7495000000000001</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.297</v>
+        <v>-0.2327</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.5581</v>
+        <v>-0.2327</v>
       </c>
       <c r="O19" t="n">
-        <v>0.261</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.6959</v>
+        <v>-1.8556</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.1598</v>
+        <v>-2.3195</v>
       </c>
       <c r="R19" t="n">
         <v>0.4639</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.2647</v>
+        <v>0.3971</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.5149</v>
+        <v>-0.1177</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.7499</v>
+        <v>0.5149</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.2836</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.2836</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-4.3808</v>
+        <v>-4.2064</v>
       </c>
       <c r="E20" t="n">
-        <v>-3.0481</v>
+        <v>-2.9302</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.3327</v>
+        <v>-1.2762</v>
       </c>
       <c r="G20" t="n">
         <v>-2.0971</v>
@@ -2014,13 +2014,13 @@
         <v>0.6959</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.6058</v>
+        <v>-0.4314</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.8136</v>
+        <v>-0.6956</v>
       </c>
       <c r="U20" t="n">
-        <v>0.2078</v>
+        <v>0.2642</v>
       </c>
       <c r="V20" t="n">
         <v>-1.214</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-13.2351</v>
+        <v>-10.8761</v>
       </c>
       <c r="E21" t="n">
-        <v>-12.2362</v>
+        <v>-12.2363</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.9991000000000001</v>
+        <v>1.360099999999999</v>
       </c>
       <c r="G21" t="n">
         <v>-5.849</v>
@@ -2062,10 +2062,10 @@
         <v>-12.959</v>
       </c>
       <c r="I21" t="n">
-        <v>7.109799999999998</v>
+        <v>7.1098</v>
       </c>
       <c r="J21" t="n">
-        <v>0.6602000000000003</v>
+        <v>0.6601999999999995</v>
       </c>
       <c r="K21" t="n">
         <v>-6.2148</v>
@@ -2077,13 +2077,13 @@
         <v>-6.5091</v>
       </c>
       <c r="N21" t="n">
-        <v>-6.7442</v>
+        <v>-6.744199999999999</v>
       </c>
       <c r="O21" t="n">
-        <v>0.2348000000000001</v>
+        <v>0.2348000000000002</v>
       </c>
       <c r="P21" t="n">
-        <v>1.1598</v>
+        <v>1.159799999999999</v>
       </c>
       <c r="Q21" t="n">
         <v>-11.5978</v>
@@ -2092,13 +2092,13 @@
         <v>12.7575</v>
       </c>
       <c r="S21" t="n">
-        <v>-5.267200000000001</v>
+        <v>-2.9083</v>
       </c>
       <c r="T21" t="n">
-        <v>-5.6188</v>
+        <v>-5.6186</v>
       </c>
       <c r="U21" t="n">
-        <v>0.3514999999999999</v>
+        <v>2.7105</v>
       </c>
       <c r="V21" t="n">
         <v>-3.2787</v>
